--- a/data/datasets/test_reports/PCRTA/PCRTA_of_feature_group_2.xlsx
+++ b/data/datasets/test_reports/PCRTA/PCRTA_of_feature_group_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,11 @@
           <t>conditional_relevance_for_gamma</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>conditional_relevance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -475,16 +480,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.913767703809479</v>
+        <v>-1.913768048688921</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1748752901267325</v>
+        <v>0.1748750745994053</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7009133009543334</v>
+        <v>0.7009133500421414</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2751082558924747</v>
+        <v>0.2751083076224808</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -494,6 +499,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>🔴</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>🟡</t>
         </is>
       </c>
     </row>
@@ -507,16 +517,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.3141901232125234</v>
+        <v>-0.3141907232040317</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.393413119670933</v>
+        <v>-4.393417686965675</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3927599939485462</v>
+        <v>0.3927601359293397</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9114825846009419</v>
+        <v>0.9114827859119246</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -524,6 +534,11 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
@@ -539,16 +554,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-9.01832075109666</v>
+        <v>-9.018282192307847</v>
       </c>
       <c r="D4" t="n">
-        <v>1.584725333610032</v>
+        <v>1.58472544151477</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9912173045793887</v>
+        <v>0.9912171352595467</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02720188552610403</v>
+        <v>0.02720187723073741</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -558,6 +573,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>🟢</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>🔴</t>
         </is>
       </c>
     </row>
@@ -571,16 +591,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-2.323562474502485</v>
+        <v>-2.323563570114595</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03529920157509186</v>
+        <v>0.03529945412269463</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7543351479611082</v>
+        <v>0.754335278202087</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3087700291838529</v>
+        <v>0.3087699680939854</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -588,6 +608,11 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
@@ -603,16 +628,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-5.320670829213945</v>
+        <v>-5.320671422099274</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7901477815965857</v>
+        <v>-0.7901477483256497</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9442535425280117</v>
+        <v>0.9442535590267214</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5005464085136527</v>
+        <v>0.5005464013874185</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -620,6 +645,11 @@
         </is>
       </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
@@ -635,16 +665,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.054551071869333</v>
+        <v>1.054551080498076</v>
       </c>
       <c r="D7" t="n">
-        <v>1.840605981707899</v>
+        <v>1.84060603110984</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09020640496816545</v>
+        <v>0.09020640357984733</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01207137954988657</v>
+        <v>0.01207137743039421</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -652,6 +682,11 @@
         </is>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
@@ -667,16 +702,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.8156508999862249</v>
+        <v>-0.8156507940543103</v>
       </c>
       <c r="D8" t="n">
-        <v>2.484074806543752</v>
+        <v>2.484075112338628</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5059897574108683</v>
+        <v>0.505989734880661</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0005348615751418206</v>
+        <v>0.0005348605228172598</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -684,6 +719,11 @@
         </is>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
@@ -699,16 +739,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.4368249724839874</v>
+        <v>0.4368249818822947</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.040274968676956</v>
+        <v>-1.040275572451395</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2134627110181541</v>
+        <v>0.2134627088667709</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5522186530106664</v>
+        <v>0.5522187730051553</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -718,6 +758,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>🔴</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>🟡</t>
         </is>
       </c>
     </row>
@@ -731,16 +776,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.276107865205019</v>
+        <v>1.276107917083541</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.858173323059445</v>
+        <v>-1.858173686830524</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05838529793756475</v>
+        <v>0.05838529140574211</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6929061833062469</v>
+        <v>0.6929062363183829</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -750,6 +795,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>🔴</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>🟡</t>
         </is>
       </c>
     </row>
@@ -763,16 +813,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-3.616734597000992</v>
+        <v>-3.616735026811288</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3994561522790582</v>
+        <v>0.3994559571945492</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8697928994426096</v>
+        <v>0.8697929271750502</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2220592617909918</v>
+        <v>0.2220593068834772</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -780,6 +830,11 @@
         </is>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
@@ -795,16 +850,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-3.665483267415631</v>
+        <v>-3.665484437059213</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.924640943356122</v>
+        <v>-4.924643539203569</v>
       </c>
       <c r="E12" t="n">
-        <v>0.872901260123333</v>
+        <v>0.8729013338215053</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9320730303751564</v>
+        <v>0.9320731183258181</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -812,6 +867,11 @@
         </is>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
@@ -827,16 +887,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1.079095207463354</v>
+        <v>-1.079093606929625</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5071919674515201</v>
+        <v>0.5071920719204404</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5598852589613097</v>
+        <v>0.5598849448789961</v>
       </c>
       <c r="F13" t="n">
-        <v>0.197519422655335</v>
+        <v>0.197519399243626</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -846,6 +906,11 @@
       <c r="H13" t="inlineStr">
         <is>
           <t>🔴</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>🟡</t>
         </is>
       </c>
     </row>
@@ -859,16 +924,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-4.318949037575336</v>
+        <v>-4.318950312210734</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.97055327288246</v>
+        <v>-2.970553814429638</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9081393827657882</v>
+        <v>0.9081394410508106</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8208594609014074</v>
+        <v>0.8208595085845258</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -878,6 +943,11 @@
       <c r="H14" t="inlineStr">
         <is>
           <t>🔴</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>🟡</t>
         </is>
       </c>
     </row>
@@ -891,16 +961,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-6.964820022642169</v>
+        <v>-6.964816668834803</v>
       </c>
       <c r="D15" t="n">
-        <v>1.016146713164575</v>
+        <v>1.016146724876474</v>
       </c>
       <c r="E15" t="n">
-        <v>0.975482270650172</v>
+        <v>0.9754822295492097</v>
       </c>
       <c r="F15" t="n">
-        <v>0.09649556002627391</v>
+        <v>0.09649555807501242</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -910,6 +980,11 @@
       <c r="H15" t="inlineStr">
         <is>
           <t>🔴</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>🟡</t>
         </is>
       </c>
     </row>
